--- a/prova_real/trimestre_08/resultado_T8.xlsx
+++ b/prova_real/trimestre_08/resultado_T8.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -576,32 +576,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13.64</v>
+        <v>7.81</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44</v>
+        <v>41.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.4</v>
+        <v>4.39</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>12.05</v>
+        <v>9.73</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.1404</v>
+        <v>-0.2009</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>2588.24</v>
+        <v>2964.29</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>8470.59</v>
+        <v>10107.14</v>
       </c>
     </row>
     <row r="3">
@@ -650,17 +650,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.75</v>
+        <v>10.46</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>36.79</v>
+        <v>29.71</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3.92</v>
+        <v>1.32</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>8.84</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>2164.12</v>
+        <v>2122.14</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>8046.47</v>
+        <v>9265</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11.23</v>
+        <v>4.41</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>32.14</v>
+        <v>25.76</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.52</v>
+        <v>0.95</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>10.58</v>
+        <v>10.22</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-0.2661</v>
+        <v>0.156</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1890.59</v>
+        <v>1840</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>7772.94</v>
+        <v>8982.860000000001</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>22.94</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.51</v>
+        <v>23.84</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2.26</v>
+        <v>1.22</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>24.86</v>
+        <v>3.12</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-6.6017</v>
+        <v>0.6796</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1677.06</v>
+        <v>1702.86</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>7559.41</v>
+        <v>8845.709999999999</v>
       </c>
     </row>
     <row r="6">
@@ -872,32 +872,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.4</v>
+        <v>12.58</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>28.05</v>
+        <v>22.87</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>10.15</v>
+        <v>4.25</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.0672</v>
+        <v>0.61</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1650</v>
+        <v>1633.57</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>7532.35</v>
+        <v>8776.43</v>
       </c>
     </row>
     <row r="7">
@@ -946,32 +946,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6.24</v>
+        <v>6.35</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>23.9</v>
+        <v>21.58</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.46</v>
+        <v>1.76</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>5.14</v>
+        <v>19.39</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2149</v>
+        <v>-3.8592</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1405.88</v>
+        <v>1541.43</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>7288.24</v>
+        <v>8684.290000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1020,32 +1020,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13.15</v>
+        <v>30.4</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.21</v>
+        <v>21.56</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.19</v>
+        <v>14.64</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6509</v>
+        <v>-2.9099</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1365.29</v>
+        <v>1540</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>7247.65</v>
+        <v>8682.860000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>58.1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30.41</v>
+        <v>8.98</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>21.54</v>
+        <v>19.34</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>13.53</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-2.6506</v>
+        <v>0.3548</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>1267.06</v>
+        <v>1381.43</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>7149.41</v>
+        <v>8524.290000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1168,32 +1168,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>4.16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.05</v>
+        <v>18.55</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.85</v>
+        <v>0.95</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>15.89</v>
+        <v>3.49</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-3.3501</v>
+        <v>0.3358</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>1120.59</v>
+        <v>1325</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>7002.94</v>
+        <v>8467.860000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.65</v>
+        <v>10.21</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>16.31</v>
+        <v>18.07</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>3.13</v>
+        <v>6.54</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.2209</v>
+        <v>-0.4875</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>959.41</v>
+        <v>1290.71</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>6841.76</v>
+        <v>8433.57</v>
       </c>
     </row>
     <row r="12">
@@ -1316,32 +1316,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.91</v>
+        <v>7.62</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.54</v>
+        <v>16.16</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.43</v>
+        <v>2.47</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>7.84</v>
+        <v>13.82</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-1.3744</v>
+        <v>-2.0129</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>855.29</v>
+        <v>1154.29</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>6737.65</v>
+        <v>8297.139999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>59.7</v>
+        <v>62.9</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.1</v>
+        <v>7.16</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14.51</v>
+        <v>13.46</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3.22</v>
+        <v>1.24</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>18.55</v>
+        <v>4.56</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-15.7098</v>
+        <v>-0.8585</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>853.53</v>
+        <v>961.4299999999999</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>6735.88</v>
+        <v>8104.29</v>
       </c>
     </row>
     <row r="14">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>62.9</v>
+        <v>58.1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.28</v>
+        <v>4.91</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.72</v>
+        <v>7.61</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.93</v>
+        <v>1.92</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.45</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.2407</v>
+        <v>-8.1395</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>748.24</v>
+        <v>543.5700000000001</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>6630.59</v>
+        <v>7686.43</v>
       </c>
     </row>
     <row r="15">
@@ -1538,32 +1538,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.28</v>
+        <v>15.94</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11.71</v>
+        <v>3.39</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1586,244 +1586,244 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6</v>
+        <v>3.04</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>7.84</v>
+        <v>24.68</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>-3.5425</v>
+        <v>-177.2347</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>688.8200000000001</v>
+        <v>242.14</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>6571.18</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>BBAS3</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>-15.9959</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>664.71</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>6547.06</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>SBFG3</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>PSSA3</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>-2.1905</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>551.1799999999999</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>6433.53</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>CURY3</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CXSE3</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>-3.79</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>-122.8263</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>-222.94</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>5659.41</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>MBRF3</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MBRF3</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1856,10 +1856,10 @@
         <v>53.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11.3</v>
+        <v>8.16</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>22.41</v>
+        <v>16.85</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.51</v>
+        <v>1.58</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>4.89</v>
+        <v>7.57</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.0625</v>
+        <v>-1.3996</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0</v>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1930,10 +1930,10 @@
         <v>53.2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.91</v>
+        <v>4.42</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>17.94</v>
+        <v>11.42</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>9.31</v>
+        <v>9.93</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-3.1574</v>
+        <v>-2.9783</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0</v>
@@ -1982,17 +1982,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2004,10 +2004,10 @@
         <v>53.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4.26</v>
+        <v>6.61</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.37</v>
+        <v>11.27</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>7.93</v>
+        <v>6.51</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-1.2066</v>
+        <v>-1.6691</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2078,10 +2078,10 @@
         <v>53.2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>5.2</v>
+        <v>16.99</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>11.84</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.71</v>
+        <v>13.96</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-5.1025</v>
+        <v>-10.99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
@@ -2130,17 +2130,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>KLBN4</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2152,10 +2152,10 @@
         <v>53.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.36</v>
+        <v>11.62</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.97</v>
+        <v>7.71</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.21</v>
+        <v>1.35</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>5.8</v>
+        <v>19.63</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-3.9055</v>
+        <v>-14.2639</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0</v>
@@ -2204,17 +2204,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2226,10 +2226,10 @@
         <v>53.2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>5.82</v>
+        <v>5.48</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>5.47</v>
+        <v>7.45</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>4.11</v>
+        <v>0.21</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>20.06</v>
+        <v>5.79</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-32.4505</v>
+        <v>-2.9965</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0</v>
@@ -2271,224 +2271,224 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>CASH3</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>-19.09</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>-5.3386</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="4" t="n">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SMFT3</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>-22.5637</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>IGTI11</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>-1.9681</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="4" t="n">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>ODPV3</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-5.5301</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>VIVT3</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>-0.7531</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="4" t="n">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SAUD3</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>-5.5301</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2500,36 +2500,36 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-24</v>
+        <v>3.89</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.23</v>
+        <v>19.81</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.78</v>
+        <v>4.03</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.2133</v>
+        <v>0.211</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
@@ -2574,36 +2574,36 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.57</v>
+        <v>-3.81</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14.55</v>
+        <v>19.68</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.35</v>
+        <v>1.21</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.33</v>
+        <v>27.3</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.1687</v>
+        <v>-11.0565</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2648,36 +2648,36 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>CASH3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.9</v>
+        <v>-21.54</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13.44</v>
+        <v>18.69</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.75</v>
+        <v>0.93</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>12.21</v>
+        <v>15.68</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.9359</v>
+        <v>-8.2958</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
@@ -2722,36 +2722,36 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-11.16</v>
+        <v>0.26</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.1</v>
+        <v>16.79</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.59</v>
+        <v>2.54</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>19.05</v>
+        <v>7.84</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-7.995</v>
+        <v>-1.7655</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -2796,17 +2796,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2815,17 +2815,17 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.03</v>
+        <v>3.76</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>16.52</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.51</v>
+        <v>2.67</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>34.05</v>
+        <v>15.38</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-18.6976</v>
+        <v>-8.365600000000001</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
@@ -2870,36 +2870,36 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.98</v>
+        <v>-1.13</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.81</v>
+        <v>15.8</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.31</v>
+        <v>0.84</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.44</v>
+        <v>8.75</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.0148</v>
+        <v>-0.4418</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>0</v>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.19</v>
+        <v>0.35</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.94</v>
+        <v>15.02</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.15</v>
+        <v>6.39</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.473</v>
+        <v>-0.759</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -3018,36 +3018,36 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-35.68</v>
+        <v>1.65</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.91</v>
+        <v>14.19</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>38.17</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.6608</v>
+        <v>-3.3722</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -3092,17 +3092,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3114,14 +3114,14 @@
         <v>54.8</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.34</v>
+        <v>-26.78</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>3.77</v>
+        <v>13.98</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>4.19</v>
+        <v>12.45</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>-1.9411</v>
+        <v>-3.1532</v>
       </c>
       <c r="P36" s="4" t="n">
         <v>0</v>
@@ -3166,32 +3166,32 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3.7</v>
+        <v>12.06</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>2.8</v>
+        <v>6.09</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>-1.4154</v>
+        <v>-1.0206</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,32 +3240,32 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>GRND3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-2.7</v>
+        <v>-4.89</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.61</v>
+        <v>10.82</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.09</v>
+        <v>4.11</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2.29</v>
+        <v>37.2</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.2488</v>
+        <v>-23.0121</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,32 +3314,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-7.88</v>
+        <v>-22.02</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.54</v>
+        <v>10.29</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>6.25</v>
+        <v>11.59</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-0.9399</v>
+        <v>-3.9868</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,17 +3388,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -3410,19 +3410,19 @@
         <v>56.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-18.37</v>
+        <v>3.16</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.49</v>
+        <v>10</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.31</v>
+        <v>1.2</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>16.2</v>
+        <v>4.27</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-10.2393</v>
+        <v>-1.6179</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,32 +3462,32 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-10.16</v>
+        <v>-10.11</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-1.64</v>
+        <v>9.82</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>1.79</v>
+        <v>5.5</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>4.74</v>
+        <v>18.75</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-3.8783</v>
+        <v>-8.7941</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,41 +3536,41 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-2.49</v>
+        <v>1.6</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-2.82</v>
+        <v>9.01</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>4.76</v>
+        <v>3.08</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>43.01</v>
+        <v>7.2</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-30.5554</v>
+        <v>-1.0589</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3610,41 +3610,41 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GGBR3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-0.67</v>
+        <v>1.37</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-3.27</v>
+        <v>7.36</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>3.26</v>
+        <v>2.36</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-1.3032</v>
+        <v>0.1442</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3684,17 +3684,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-7.97</v>
+        <v>1.38</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-5.08</v>
+        <v>4.4</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>4.22</v>
+        <v>0.74</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>10.9</v>
+        <v>2.55</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-3.5619</v>
+        <v>-0.5472</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -3758,32 +3758,32 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>59.7</v>
+        <v>53.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-111.54</v>
+        <v>-8.56</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-7.97</v>
+        <v>3.95</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>12.04</v>
+        <v>2.12</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>56.99</v>
+        <v>4.59</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>-16.8474</v>
+        <v>-1.5281</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -3832,32 +3832,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>59.7</v>
+        <v>53.2</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-4.02</v>
+        <v>-3.08</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-8.859999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -3866,12 +3866,12 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>1</v>
+        <v>0.11</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.93</v>
+        <v>2.59</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.3566</v>
+        <v>-0.6297</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -3906,41 +3906,41 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>SEQL3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-15.56</v>
+        <v>0.64</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-11.39</v>
+        <v>1.69</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>16.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>37.67</v>
+        <v>3.91</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-1.6391</v>
+        <v>-1.7214</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -3980,32 +3980,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>62.9</v>
+        <v>53.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-61.97</v>
+        <v>-7.83</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-20.26</v>
+        <v>0.39</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>1.8</v>
+        <v>0.46</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>32.86</v>
+        <v>6.47</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-4.5046</v>
+        <v>-0.9802</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
@@ -4054,32 +4054,32 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>PMAM3</t>
+          <t>GGBR3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-29.14</v>
+        <v>-0.9</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-20.31</v>
+        <v>-0.33</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>5.24</v>
+        <v>3.04</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>0.0613</v>
+        <v>-1.0858</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>0</v>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-14.61</v>
+        <v>-118.18</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-25.15</v>
+        <v>-1.59</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>3.08</v>
+        <v>12.94</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>30.2</v>
+        <v>61.7</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>-15.8929</v>
+        <v>-18.7847</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>56.5</v>
+        <v>61.3</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-19.63</v>
+        <v>-11.05</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-29</v>
+        <v>-2.28</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.23</v>
+        <v>1.77</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>16.3</v>
+        <v>4.67</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>-1.7909</v>
+        <v>-2.8949</v>
       </c>
       <c r="P51" s="4" t="n">
         <v>0</v>
@@ -4276,32 +4276,32 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-20.43</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-29.57</v>
+        <v>-4.17</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.72</v>
+        <v>3.39</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>10.59</v>
+        <v>8.77</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.1281</v>
+        <v>-2.3663</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -4350,69 +4350,809 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
+          <t>SEQL3</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-17.42</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>-1.449</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-61.27</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>-14.6245</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>HBOR3</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>-21.7957</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>DASA3</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-75.65000000000001</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>-3.7405</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>YDUQ3</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-16.79</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>-21.12</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>-17.557</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>COGN3</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-22.78</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>-24.74</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>-0.666</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>PMAM3</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-30.72</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ONCO3</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>-21.49</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>-33.7</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>-0.0334</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>AMAR3</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>-58.29</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>-30.68</v>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-63.6</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>-34.66</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v>-8.0174</v>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="4" t="n">
+      <c r="M63" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>-10.7338</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4427,7 +5167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4550,32 +5290,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13.64</v>
+        <v>7.81</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44</v>
+        <v>41.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -4598,22 +5338,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.4</v>
+        <v>4.39</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>12.05</v>
+        <v>9.73</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.1404</v>
+        <v>-0.2009</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>2588.24</v>
+        <v>2964.29</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>8470.59</v>
+        <v>10107.14</v>
       </c>
     </row>
     <row r="3">
@@ -4624,17 +5364,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4643,13 +5383,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.75</v>
+        <v>10.46</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>36.79</v>
+        <v>29.71</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -4672,22 +5412,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3.92</v>
+        <v>1.32</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>8.84</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>2164.12</v>
+        <v>2122.14</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>8046.47</v>
+        <v>9265</v>
       </c>
     </row>
     <row r="4">
@@ -4698,17 +5438,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4717,13 +5457,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11.23</v>
+        <v>4.41</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>32.14</v>
+        <v>25.76</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -4746,22 +5486,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.52</v>
+        <v>0.95</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>10.58</v>
+        <v>10.22</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-0.2661</v>
+        <v>0.156</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1890.59</v>
+        <v>1840</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>7772.94</v>
+        <v>8982.860000000001</v>
       </c>
     </row>
     <row r="5">
@@ -4772,17 +5512,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4791,13 +5531,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>22.94</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.51</v>
+        <v>23.84</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -4820,22 +5560,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2.26</v>
+        <v>1.22</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>24.86</v>
+        <v>3.12</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-6.6017</v>
+        <v>0.6796</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1677.06</v>
+        <v>1702.86</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>7559.41</v>
+        <v>8845.709999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4846,32 +5586,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.4</v>
+        <v>12.58</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>28.05</v>
+        <v>22.87</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -4894,22 +5634,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>10.15</v>
+        <v>4.25</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.0672</v>
+        <v>0.61</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1650</v>
+        <v>1633.57</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>7532.35</v>
+        <v>8776.43</v>
       </c>
     </row>
     <row r="7">
@@ -4920,32 +5660,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6.24</v>
+        <v>6.35</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>23.9</v>
+        <v>21.58</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -4968,22 +5708,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.46</v>
+        <v>1.76</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>5.14</v>
+        <v>19.39</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2149</v>
+        <v>-3.8592</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1405.88</v>
+        <v>1541.43</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>7288.24</v>
+        <v>8684.290000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4994,32 +5734,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13.15</v>
+        <v>30.4</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.21</v>
+        <v>21.56</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -5042,22 +5782,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.19</v>
+        <v>14.64</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6509</v>
+        <v>-2.9099</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1365.29</v>
+        <v>1540</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>7247.65</v>
+        <v>8682.860000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5068,17 +5808,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5090,10 +5830,10 @@
         <v>58.1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30.41</v>
+        <v>8.98</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>21.54</v>
+        <v>19.34</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -5116,22 +5856,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>13.53</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-2.6506</v>
+        <v>0.3548</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>1267.06</v>
+        <v>1381.43</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>7149.41</v>
+        <v>8524.290000000001</v>
       </c>
     </row>
     <row r="10">
@@ -5142,32 +5882,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>4.16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.05</v>
+        <v>18.55</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -5190,22 +5930,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.85</v>
+        <v>0.95</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>15.89</v>
+        <v>3.49</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-3.3501</v>
+        <v>0.3358</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>1120.59</v>
+        <v>1325</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>7002.94</v>
+        <v>8467.860000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5216,32 +5956,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.65</v>
+        <v>10.21</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>16.31</v>
+        <v>18.07</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -5264,22 +6004,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>3.13</v>
+        <v>6.54</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.2209</v>
+        <v>-0.4875</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>959.41</v>
+        <v>1290.71</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>6841.76</v>
+        <v>8433.57</v>
       </c>
     </row>
     <row r="12">
@@ -5290,32 +6030,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.91</v>
+        <v>7.62</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.54</v>
+        <v>16.16</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -5338,22 +6078,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.43</v>
+        <v>2.47</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>7.84</v>
+        <v>13.82</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-1.3744</v>
+        <v>-2.0129</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>855.29</v>
+        <v>1154.29</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>6737.65</v>
+        <v>8297.139999999999</v>
       </c>
     </row>
     <row r="13">
@@ -5364,17 +6104,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5383,13 +6123,13 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>59.7</v>
+        <v>62.9</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.1</v>
+        <v>7.16</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14.51</v>
+        <v>13.46</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -5412,22 +6152,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3.22</v>
+        <v>1.24</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>18.55</v>
+        <v>4.56</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-15.7098</v>
+        <v>-0.8585</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>853.53</v>
+        <v>961.4299999999999</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>6735.88</v>
+        <v>8104.29</v>
       </c>
     </row>
     <row r="14">
@@ -5438,17 +6178,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5457,13 +6197,13 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>62.9</v>
+        <v>58.1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.28</v>
+        <v>4.91</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.72</v>
+        <v>7.61</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -5486,22 +6226,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.93</v>
+        <v>1.92</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.45</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.2407</v>
+        <v>-8.1395</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>748.24</v>
+        <v>543.5700000000001</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>6630.59</v>
+        <v>7686.43</v>
       </c>
     </row>
     <row r="15">
@@ -5512,32 +6252,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.28</v>
+        <v>15.94</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11.71</v>
+        <v>3.39</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -5560,244 +6300,22 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6</v>
+        <v>3.04</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>7.84</v>
+        <v>24.68</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>-3.5425</v>
+        <v>-177.2347</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>5882.35</v>
+        <v>7142.86</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>688.8200000000001</v>
+        <v>242.14</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>6571.18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>BBAS3</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>-15.9959</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>664.71</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>6547.06</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>PSSA3</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>-2.1905</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>551.1799999999999</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>6433.53</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>T-8</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CXSE3</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>-3.79</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>-122.8263</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>5882.35</v>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>-222.94</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>5659.41</v>
+        <v>7385</v>
       </c>
     </row>
   </sheetData>
